--- a/rosters/2026-05.xlsx
+++ b/rosters/2026-05.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rubesh S\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Amirdeshwara\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="8130"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="11220"/>
   </bookViews>
   <sheets>
     <sheet name="May" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="84">
   <si>
     <t>Date</t>
   </si>
@@ -35,9 +35,6 @@
     <t>Morning Shift 6 AM 3 PM</t>
   </si>
   <si>
-    <t xml:space="preserve">Afternoon Shift 2 PM 11 PM </t>
-  </si>
-  <si>
     <t>Night Shift 10 PM 7 AM</t>
   </si>
   <si>
@@ -164,10 +161,121 @@
     <t>Shree, Valai</t>
   </si>
   <si>
-    <t>Shree, Priya, Bala</t>
-  </si>
-  <si>
     <t>Rubesh, Sharan</t>
+  </si>
+  <si>
+    <t>Afternoon Shift 2 PM 11 PM</t>
+  </si>
+  <si>
+    <t>Priya, Bala, Valai</t>
+  </si>
+  <si>
+    <t>Amirdeshwara, Valai, Bala</t>
+  </si>
+  <si>
+    <t>Sharan, Rubesh, Shiyam</t>
+  </si>
+  <si>
+    <t>Amirdeshwara, Priya, Valai, Bala</t>
+  </si>
+  <si>
+    <t>Maveera, Rubesh, Shiyam</t>
+  </si>
+  <si>
+    <t>Sharan</t>
+  </si>
+  <si>
+    <t>Maveera, Sharan, Shiyam</t>
+  </si>
+  <si>
+    <t>Amirdeshwara, Rubesh, Priya, Valai</t>
+  </si>
+  <si>
+    <t>Bala</t>
+  </si>
+  <si>
+    <t>Amirdeshwara, Rubesh, Priya</t>
+  </si>
+  <si>
+    <t>Maveera, Shiyam</t>
+  </si>
+  <si>
+    <t>Shree, Bala</t>
+  </si>
+  <si>
+    <t>Sharan, Valai</t>
+  </si>
+  <si>
+    <t>Rubesh, Priya</t>
+  </si>
+  <si>
+    <t>Maveera, Shiyam, Valai</t>
+  </si>
+  <si>
+    <t>Sharan, Bala</t>
+  </si>
+  <si>
+    <t>Shree, Amirdeshwara</t>
+  </si>
+  <si>
+    <t>Amirdeshwara, Valai</t>
+  </si>
+  <si>
+    <t>Shree, Maveera</t>
+  </si>
+  <si>
+    <t>Rubesh, Maveera, Shiyam</t>
+  </si>
+  <si>
+    <t>Amirdeshwara, Shree, Valai</t>
+  </si>
+  <si>
+    <t>Priya, Shiyam</t>
+  </si>
+  <si>
+    <t>Amirdeshwara, Shree, Priya, Valai</t>
+  </si>
+  <si>
+    <t>Shree, Priya, Valai</t>
+  </si>
+  <si>
+    <t>Amirdeshwara, Rubesh</t>
+  </si>
+  <si>
+    <t>Rubesh, Shree, Priya, Valai</t>
+  </si>
+  <si>
+    <t>Amirdeshwara, Sharan</t>
+  </si>
+  <si>
+    <t>Rubesh, Shree, Priya</t>
+  </si>
+  <si>
+    <t>Amirdeshwara</t>
+  </si>
+  <si>
+    <t>Sharan, Valai, Bala</t>
+  </si>
+  <si>
+    <t>Rubesh, Priya, Bala</t>
+  </si>
+  <si>
+    <t>Sharan, Shree, Valai</t>
+  </si>
+  <si>
+    <t>Shree, Sharan, Valai</t>
+  </si>
+  <si>
+    <t>Shree, Sharan, Valai,</t>
+  </si>
+  <si>
+    <t>Rubesh, Maveera, Shiyam, Bala</t>
+  </si>
+  <si>
+    <t>Shree, Priya, Sharan, Valai</t>
+  </si>
+  <si>
+    <t>Maveera, Bala, Shiyam</t>
   </si>
 </sst>
 </file>
@@ -183,16 +291,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Carlito"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Carlito"/>
     </font>
   </fonts>
   <fills count="3">
@@ -205,31 +314,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FF000000"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -251,19 +345,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -545,18 +636,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F16"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <dimension ref="A1:F32"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.6328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="31.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="27" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.08984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="28.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15" thickBot="1">
+    <row r="1" spans="1:6" ht="28.2" thickBot="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -567,13 +658,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="15" thickBot="1">
@@ -581,19 +672,19 @@
         <v>46143</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>9</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="15" thickBot="1">
@@ -601,19 +692,19 @@
         <v>46144</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="E3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>13</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15" thickBot="1">
@@ -621,37 +712,37 @@
         <v>46145</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="D4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="4"/>
+      <c r="E4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="3"/>
     </row>
     <row r="5" spans="1:6" ht="15" thickBot="1">
       <c r="A5" s="2">
         <v>46146</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="E5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>20</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15" thickBot="1">
@@ -659,55 +750,55 @@
         <v>46147</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="4"/>
+      <c r="E6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="3"/>
     </row>
     <row r="7" spans="1:6" ht="15" thickBot="1">
       <c r="A7" s="2">
         <v>46148</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" s="4"/>
+      <c r="E7" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="3"/>
     </row>
     <row r="8" spans="1:6" ht="15" thickBot="1">
       <c r="A8" s="2">
         <v>46149</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>9</v>
+      <c r="F8" s="3" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15" thickBot="1">
@@ -715,19 +806,19 @@
         <v>46150</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="E9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>29</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15" thickBot="1">
@@ -735,19 +826,19 @@
         <v>46151</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="E10" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="F10" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15" thickBot="1">
@@ -755,19 +846,19 @@
         <v>46152</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D11" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="F11" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15" thickBot="1">
@@ -775,19 +866,19 @@
         <v>46153</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="E12" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>39</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15" thickBot="1">
@@ -795,19 +886,19 @@
         <v>46154</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F13" s="4" t="s">
         <v>21</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15" thickBot="1">
@@ -815,19 +906,19 @@
         <v>46155</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D14" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>27</v>
+      <c r="E14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15" thickBot="1">
@@ -835,19 +926,19 @@
         <v>46156</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D15" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>44</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15" thickBot="1">
@@ -855,22 +946,341 @@
         <v>46157</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D16" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="D16" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F16" s="4" t="s">
+    </row>
+    <row r="17" spans="1:6" ht="15" thickBot="1">
+      <c r="A17" s="2">
+        <v>46158</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>10</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="15" thickBot="1">
+      <c r="A18" s="2">
+        <v>46159</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="15" thickBot="1">
+      <c r="A19" s="2">
+        <v>46160</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="15" thickBot="1">
+      <c r="A20" s="2">
+        <v>46161</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="15" thickBot="1">
+      <c r="A21" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="15" thickBot="1">
+      <c r="A22" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="15" thickBot="1">
+      <c r="A23" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="15" thickBot="1">
+      <c r="A24" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="29.4" thickBot="1">
+      <c r="A25" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F25" s="3"/>
+    </row>
+    <row r="26" spans="1:6" ht="15" thickBot="1">
+      <c r="A26" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="15" thickBot="1">
+      <c r="A27" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="15" thickBot="1">
+      <c r="A28" s="2">
+        <v>46169</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="15" thickBot="1">
+      <c r="A29" s="2">
+        <v>46170</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="15" thickBot="1">
+      <c r="A30" s="2">
+        <v>46171</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="15" thickBot="1">
+      <c r="A31" s="2">
+        <v>46172</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="15" thickBot="1">
+      <c r="A32" s="2">
+        <v>46173</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>